--- a/Docs/evaluation_logs/task_availability/task_availability_evaluation_workbook_52tasks.xlsx
+++ b/Docs/evaluation_logs/task_availability/task_availability_evaluation_workbook_52tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\-Graduation_Thesis-Import-pipeline\Docs\evaluation_logs\task_availability\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB54D3B-376C-42AD-A1C7-27139531A345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025EF544-CCDE-442B-8117-6D2C3D33C354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ground Truth" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2861" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2859" uniqueCount="467">
   <si>
     <t>case_id</t>
   </si>
@@ -661,234 +661,240 @@
     <t>Socioeconomic disadvantage impact</t>
   </si>
   <si>
+    <t>student, enrollment, assessment_result, assessment</t>
+  </si>
+  <si>
+    <t>parent education, internet_access_flag, paid_class_flag, previous_attempt_count, disadvantage_score [FE single]; avg_score [FE cross], final_outcome</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>A-G10</t>
+  </si>
+  <si>
+    <t>Consistency analysis across cohort</t>
+  </si>
+  <si>
+    <t>consistency_level [FE cross], student_count [FE cross], pct_students [FE cross], avg_weekly_stddev, avg_weekly_clicks, avg_active_weeks</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>A-G11</t>
+  </si>
+  <si>
+    <t>Weekly engagement drop detection</t>
+  </si>
+  <si>
+    <t>week_number, engagement_count; is_drop_week [FE cross], rolling_3wk_avg, drop_pct</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>A-G12</t>
+  </si>
+  <si>
+    <t>Background group pass/fail/withdrawal rate</t>
+  </si>
+  <si>
+    <t>socioeconomic_band / gender / age_group / highest_education; final_outcome</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>A-G13</t>
+  </si>
+  <si>
+    <t>Lifestyle risk across cohort</t>
+  </si>
+  <si>
+    <t>alcohol_weekday, alcohol_weekend, go_out_freq, health_status, lifestyle_risk_score [FE single]; avg_score [FE cross]</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>A-G14</t>
+  </si>
+  <si>
+    <t>Early withdrawal signal analysis</t>
+  </si>
+  <si>
+    <t>week_number, engagement_count; final_outcome, avg_clicks by outcome group</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>A-G15</t>
+  </si>
+  <si>
+    <t>Intervention priority ranking</t>
+  </si>
+  <si>
+    <t>student_id, gender, age_group, region; at_risk_score [FE cross], at_risk_label [FE cross], avg_score [FE cross], all 5 flags, final_outcome</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>A-G16</t>
+  </si>
+  <si>
+    <t>Admin action recommendation</t>
+  </si>
+  <si>
+    <t>[AI_SYNTHESIS] low_engagement_count, high_risk_count, hardest_assessment, best_resource_type, total_students</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>OULAD</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
     <t>student, enrollment, assessment_result, assessment [OULAD only]</t>
   </si>
   <si>
     <t>imd_score_numeric, disability_flag, highest_education, disadvantage_score [FE single]; avg_score [FE cross], final_outcome</t>
   </si>
   <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>A-G10</t>
-  </si>
-  <si>
-    <t>Consistency analysis across cohort</t>
-  </si>
-  <si>
-    <t>consistency_level [FE cross], student_count [FE cross], pct_students [FE cross], avg_weekly_stddev, avg_weekly_clicks, avg_active_weeks</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>A-G11</t>
-  </si>
-  <si>
-    <t>Weekly engagement drop detection</t>
-  </si>
-  <si>
-    <t>week_number, engagement_count; is_drop_week [FE cross], rolling_3wk_avg, drop_pct</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>A-G12</t>
-  </si>
-  <si>
-    <t>Background group pass/fail/withdrawal rate</t>
-  </si>
-  <si>
-    <t>socioeconomic_band / gender / age_group / highest_education; final_outcome</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>A-G13</t>
-  </si>
-  <si>
-    <t>Lifestyle risk across cohort</t>
-  </si>
-  <si>
-    <t>alcohol_weekday, alcohol_weekend, go_out_freq, health_status, lifestyle_risk_score [FE single]; avg_score [FE cross]</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>A-G14</t>
-  </si>
-  <si>
-    <t>Early withdrawal signal analysis</t>
-  </si>
-  <si>
-    <t>week_number, engagement_count; final_outcome, avg_clicks by outcome group</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>A-G15</t>
-  </si>
-  <si>
-    <t>Intervention priority ranking</t>
-  </si>
-  <si>
-    <t>student_id, gender, age_group, region; at_risk_score [FE cross], at_risk_label [FE cross], avg_score [FE cross], all 5 flags, final_outcome</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>A-G16</t>
-  </si>
-  <si>
-    <t>Admin action recommendation</t>
-  </si>
-  <si>
-    <t>[AI_SYNTHESIS] low_engagement_count, high_risk_count, hardest_assessment, best_resource_type, total_students</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>OULAD</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
     <t>98</t>
   </si>
   <si>
@@ -973,6 +979,9 @@
     <t>HIGH</t>
   </si>
   <si>
+    <t>649 students × 3 assessments across 3 weeks - strong statistical basic</t>
+  </si>
+  <si>
     <t>Required capability missing: engagement_tracking</t>
   </si>
   <si>
@@ -1015,10 +1024,7 @@
     <t>Engagementâ€“performance relationship</t>
   </si>
   <si>
-    <t>Task depends on OULAD IMD-derived disadvantage_score and score outcomes.</t>
-  </si>
-  <si>
-    <t>socioeconomic_context; disadvantage_scoring</t>
+    <t>649 students x 3 assessments across 3 weeks - strong statistical basis.</t>
   </si>
   <si>
     <t>SAMPLE_OULAD</t>
@@ -1027,6 +1033,9 @@
     <t>SAMPLE_OULAD_CLASS_CCC_2014J</t>
   </si>
   <si>
+    <t>1998 students x 9 assessments across 8 weeks - strong statistical basis.</t>
+  </si>
+  <si>
     <t>Uses UCI absence-based behavior signal; OULAD canonical data does not provide absences.</t>
   </si>
   <si>
@@ -1132,6 +1141,12 @@
     <t>disadvantage_score_students</t>
   </si>
   <si>
+    <t>disadvantage_score_students &gt;= 2</t>
+  </si>
+  <si>
+    <t>Available in dataset snapshot via UCI-derived disadvantage score</t>
+  </si>
+  <si>
     <t>assessment_result_rows</t>
   </si>
   <si>
@@ -1198,6 +1213,9 @@
     <t>resource_clickstream</t>
   </si>
   <si>
+    <t>positive_engagement_rows &gt;= 1 AND resource_type_non_null_rows &gt;= 1</t>
+  </si>
+  <si>
     <t>socioeconomic_context</t>
   </si>
   <si>
@@ -1207,6 +1225,9 @@
     <t>&gt;= 1 student with socioeconomic fields</t>
   </si>
   <si>
+    <t>Available in dataset snapshot via UCI family and socioeconomic proxies</t>
+  </si>
+  <si>
     <t>studytime_non_null_rows</t>
   </si>
   <si>
@@ -1240,6 +1261,9 @@
     <t>weeks=0, days=0</t>
   </si>
   <si>
+    <t>positive_engagement_rows &gt;= 1 AND distinct_engagement_weeks &gt;= 2</t>
+  </si>
+  <si>
     <t>submission_day=11451, due_day=8</t>
   </si>
   <si>
@@ -1264,6 +1288,9 @@
     <t>Total cases</t>
   </si>
   <si>
+    <t>Number of task x dataset pairs</t>
+  </si>
+  <si>
     <t>TP</t>
   </si>
   <si>
@@ -1309,6 +1336,9 @@
     <t>F1-score</t>
   </si>
   <si>
+    <t>2 x Precision x Recall / (Precision + Recall)</t>
+  </si>
+  <si>
     <t>Exact status correct</t>
   </si>
   <si>
@@ -1381,46 +1411,25 @@
     <t>Source logs</t>
   </si>
   <si>
+    <t>task_availability_20260621T171519Z_5d42a4.json and task_availability_20260621T171533Z_33c53a.json</t>
+  </si>
+  <si>
     <t>Capability Check</t>
   </si>
   <si>
+    <t>Supporting evidence sheet showing dataset-level capabilities, runtime metrics, and the exact boolean thresholds used by the validator.</t>
+  </si>
+  <si>
     <t>Expected status</t>
   </si>
   <si>
+    <t>Derived independently from Dataset Compatibility: compatible task-dataset pair -&gt; executable; incompatible pair -&gt; unsupported. Binary and exact-status accuracy are reported separately.</t>
+  </si>
+  <si>
     <t>Recalculation</t>
   </si>
   <si>
     <t>Machine Results comparison columns and Evaluation Summary were recalculated from the user-reviewed Ground Truth on 2026-06-19.</t>
-  </si>
-  <si>
-    <t>Number of task x dataset pairs</t>
-  </si>
-  <si>
-    <t>2 x Precision x Recall / (Precision + Recall)</t>
-  </si>
-  <si>
-    <t>649 students × 3 assessments across 3 weeks - strong statistical basic</t>
-  </si>
-  <si>
-    <t>1998 students x 9 assessments across 8 weeks - strong statistical basis.</t>
-  </si>
-  <si>
-    <t>Derived independently from Dataset Compatibility: compatible task-dataset pair -&gt; executable; incompatible pair -&gt; unsupported. Binary and exact-status accuracy are reported separately.</t>
-  </si>
-  <si>
-    <t>disadvantage_score_students &gt;= 2</t>
-  </si>
-  <si>
-    <t>positive_engagement_rows &gt;= 1 AND resource_type_non_null_rows &gt;= 1</t>
-  </si>
-  <si>
-    <t>positive_engagement_rows &gt;= 1 AND distinct_engagement_weeks &gt;= 2</t>
-  </si>
-  <si>
-    <t>task_availability_20260619T042411Z_265c90.json and task_availability_20260619T042455Z_0ef6b3.json</t>
-  </si>
-  <si>
-    <t>Supporting evidence sheet showing dataset-level capabilities, runtime metrics, and the exact boolean thresholds used by the validator.</t>
   </si>
 </sst>
 </file>
@@ -1764,12 +1773,8 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2091,8 +2096,8 @@
     <col min="6" max="6" width="59.88671875" style="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.88671875" style="8" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="8"/>
+    <col min="9" max="12" width="8.88671875" style="8" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.3">
@@ -3284,11 +3289,11 @@
       <c r="F46" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="G46" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>64</v>
+      <c r="G46" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4631,10 +4636,10 @@
         <v>209</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>210</v>
+        <v>286</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>211</v>
+        <v>287</v>
       </c>
       <c r="G98" s="10" t="s">
         <v>14</v>
@@ -4645,7 +4650,7 @@
     </row>
     <row r="99" spans="1:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B99" s="9" t="s">
         <v>241</v>
@@ -4671,7 +4676,7 @@
     </row>
     <row r="100" spans="1:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B100" s="9" t="s">
         <v>241</v>
@@ -4697,7 +4702,7 @@
     </row>
     <row r="101" spans="1:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B101" s="9" t="s">
         <v>241</v>
@@ -4723,7 +4728,7 @@
     </row>
     <row r="102" spans="1:8" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B102" s="9" t="s">
         <v>241</v>
@@ -4749,7 +4754,7 @@
     </row>
     <row r="103" spans="1:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B103" s="9" t="s">
         <v>241</v>
@@ -4775,7 +4780,7 @@
     </row>
     <row r="104" spans="1:8" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B104" s="9" t="s">
         <v>241</v>
@@ -4801,7 +4806,7 @@
     </row>
     <row r="105" spans="1:8" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B105" s="9" t="s">
         <v>241</v>
@@ -4858,7 +4863,8 @@
     <col min="21" max="21" width="27.88671875" style="8" customWidth="1"/>
     <col min="22" max="22" width="11.33203125" style="8" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="9.88671875" style="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="8.88671875" style="8"/>
+    <col min="24" max="24" width="8.88671875" style="8" customWidth="1"/>
+    <col min="25" max="16384" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" s="23" customFormat="1" x14ac:dyDescent="0.3">
@@ -4869,10 +4875,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E1" s="21" t="s">
         <v>2</v>
@@ -4881,37 +4887,37 @@
         <v>3</v>
       </c>
       <c r="G1" s="21" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H1" s="21" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="J1" s="21" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K1" s="21" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="L1" s="21" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M1" s="21" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N1" s="21" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O1" s="21" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P1" s="21" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q1" s="21" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="R1" s="21" t="s">
         <v>6</v>
@@ -4920,16 +4926,16 @@
         <v>7</v>
       </c>
       <c r="T1" s="22" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="U1" s="21" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="V1" s="21" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="W1" s="21" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4940,10 +4946,10 @@
         <v>9</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>10</v>
@@ -4959,24 +4965,24 @@
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="9"/>
       <c r="P2" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R2" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A2,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -5011,10 +5017,10 @@
         <v>9</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>17</v>
@@ -5030,24 +5036,24 @@
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
       <c r="P3" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R3" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A3,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -5082,10 +5088,10 @@
         <v>9</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>22</v>
@@ -5100,29 +5106,29 @@
         <v>27</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O4" s="9"/>
       <c r="P4" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R4" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A4,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -5157,10 +5163,10 @@
         <v>9</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>29</v>
@@ -5176,24 +5182,24 @@
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
       <c r="P5" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R5" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A5,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -5228,10 +5234,10 @@
         <v>9</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>34</v>
@@ -5247,24 +5253,24 @@
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
       <c r="P6" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R6" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A6,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -5299,10 +5305,10 @@
         <v>9</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -5318,24 +5324,24 @@
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N7" s="9"/>
       <c r="O7" s="9"/>
       <c r="P7" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R7" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A7,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -5370,10 +5376,10 @@
         <v>9</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>42</v>
@@ -5389,24 +5395,24 @@
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N8" s="9"/>
       <c r="O8" s="9"/>
       <c r="P8" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R8" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A8,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -5441,10 +5447,10 @@
         <v>9</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>46</v>
@@ -5459,29 +5465,29 @@
         <v>27</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="O9" s="9"/>
       <c r="P9" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R9" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A9,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -5516,10 +5522,10 @@
         <v>9</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>51</v>
@@ -5534,29 +5540,29 @@
         <v>27</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="O10" s="9"/>
       <c r="P10" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q10" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R10" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A10,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -5591,10 +5597,10 @@
         <v>9</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>56</v>
@@ -5610,24 +5616,24 @@
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N11" s="9"/>
       <c r="O11" s="9"/>
       <c r="P11" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R11" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A11,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -5662,10 +5668,10 @@
         <v>9</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>60</v>
@@ -5680,29 +5686,29 @@
         <v>64</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="O12" s="9"/>
       <c r="P12" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q12" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R12" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A12,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -5737,10 +5743,10 @@
         <v>9</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>66</v>
@@ -5756,24 +5762,24 @@
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N13" s="9"/>
       <c r="O13" s="9"/>
       <c r="P13" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R13" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A13,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -5808,10 +5814,10 @@
         <v>9</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>71</v>
@@ -5826,29 +5832,29 @@
         <v>27</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="O14" s="9"/>
       <c r="P14" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R14" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A14,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -5883,10 +5889,10 @@
         <v>9</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>76</v>
@@ -5901,29 +5907,29 @@
         <v>64</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="O15" s="9"/>
       <c r="P15" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R15" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A15,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -5958,10 +5964,10 @@
         <v>9</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>81</v>
@@ -5976,29 +5982,29 @@
         <v>64</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="O16" s="9"/>
       <c r="P16" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q16" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R16" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A16,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -6033,10 +6039,10 @@
         <v>9</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>85</v>
@@ -6052,24 +6058,24 @@
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N17" s="9"/>
       <c r="O17" s="9"/>
       <c r="P17" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R17" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A17,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -6104,10 +6110,10 @@
         <v>9</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>90</v>
@@ -6123,24 +6129,24 @@
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N18" s="9"/>
       <c r="O18" s="9"/>
       <c r="P18" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R18" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A18,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -6175,10 +6181,10 @@
         <v>9</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>95</v>
@@ -6194,24 +6200,24 @@
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N19" s="9"/>
       <c r="O19" s="9"/>
       <c r="P19" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R19" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A19,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -6246,10 +6252,10 @@
         <v>9</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>99</v>
@@ -6265,24 +6271,24 @@
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N20" s="9"/>
       <c r="O20" s="9"/>
       <c r="P20" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R20" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A20,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -6317,10 +6323,10 @@
         <v>9</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>104</v>
@@ -6336,24 +6342,24 @@
       </c>
       <c r="I21" s="9"/>
       <c r="J21" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N21" s="9"/>
       <c r="O21" s="9"/>
       <c r="P21" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R21" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A21,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -6388,10 +6394,10 @@
         <v>9</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>109</v>
@@ -6406,29 +6412,29 @@
         <v>27</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M22" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O22" s="9"/>
       <c r="P22" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R22" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A22,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -6463,10 +6469,10 @@
         <v>9</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>113</v>
@@ -6481,29 +6487,29 @@
         <v>27</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="O23" s="9"/>
       <c r="P23" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q23" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R23" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A23,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -6538,10 +6544,10 @@
         <v>9</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>117</v>
@@ -6556,29 +6562,29 @@
         <v>27</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M24" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O24" s="9"/>
       <c r="P24" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q24" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R24" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A24,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -6613,10 +6619,10 @@
         <v>9</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>122</v>
@@ -6632,24 +6638,24 @@
       </c>
       <c r="I25" s="9"/>
       <c r="J25" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M25" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N25" s="9"/>
       <c r="O25" s="9"/>
       <c r="P25" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R25" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A25,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -6684,10 +6690,10 @@
         <v>9</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>125</v>
@@ -6702,29 +6708,29 @@
         <v>27</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M26" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N26" s="9" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="O26" s="9"/>
       <c r="P26" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R26" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A26,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -6759,10 +6765,10 @@
         <v>9</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>129</v>
@@ -6778,24 +6784,24 @@
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N27" s="9"/>
       <c r="O27" s="9"/>
       <c r="P27" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R27" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A27,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -6830,10 +6836,10 @@
         <v>9</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>132</v>
@@ -6849,24 +6855,24 @@
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M28" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N28" s="9"/>
       <c r="O28" s="9"/>
       <c r="P28" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R28" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A28,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -6901,10 +6907,10 @@
         <v>9</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>135</v>
@@ -6919,29 +6925,29 @@
         <v>64</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M29" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="O29" s="9"/>
       <c r="P29" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R29" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A29,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -6976,10 +6982,10 @@
         <v>9</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>138</v>
@@ -6995,24 +7001,24 @@
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M30" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N30" s="9"/>
       <c r="O30" s="9"/>
       <c r="P30" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R30" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A30,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -7047,10 +7053,10 @@
         <v>9</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>142</v>
@@ -7065,29 +7071,29 @@
         <v>27</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M31" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O31" s="9"/>
       <c r="P31" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R31" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A31,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -7122,10 +7128,10 @@
         <v>9</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>147</v>
@@ -7141,24 +7147,24 @@
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M32" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N32" s="9"/>
       <c r="O32" s="9"/>
       <c r="P32" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q32" s="18" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R32" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A32,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -7193,10 +7199,10 @@
         <v>9</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>151</v>
@@ -7211,29 +7217,29 @@
         <v>27</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M33" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O33" s="9"/>
       <c r="P33" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R33" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A33,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -7268,10 +7274,10 @@
         <v>9</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>155</v>
@@ -7286,29 +7292,29 @@
         <v>27</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L34" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M34" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O34" s="9"/>
       <c r="P34" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q34" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R34" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A34,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -7343,10 +7349,10 @@
         <v>9</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>159</v>
@@ -7362,24 +7368,24 @@
       </c>
       <c r="I35" s="9"/>
       <c r="J35" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L35" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M35" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N35" s="9"/>
       <c r="O35" s="9"/>
       <c r="P35" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q35" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R35" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A35,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -7414,10 +7420,10 @@
         <v>9</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>164</v>
@@ -7433,24 +7439,24 @@
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L36" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M36" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N36" s="9"/>
       <c r="O36" s="9"/>
       <c r="P36" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q36" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R36" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A36,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -7485,10 +7491,10 @@
         <v>9</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>168</v>
@@ -7503,29 +7509,29 @@
         <v>27</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K37" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M37" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="O37" s="9"/>
       <c r="P37" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q37" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R37" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A37,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -7560,10 +7566,10 @@
         <v>9</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>172</v>
@@ -7578,29 +7584,29 @@
         <v>27</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M38" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N38" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O38" s="9"/>
       <c r="P38" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q38" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R38" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A38,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -7635,16 +7641,16 @@
         <v>9</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>176</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>26</v>
@@ -7653,29 +7659,29 @@
         <v>27</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L39" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O39" s="9"/>
       <c r="P39" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q39" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R39" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A39,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -7710,10 +7716,10 @@
         <v>9</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>180</v>
@@ -7729,24 +7735,24 @@
       </c>
       <c r="I40" s="9"/>
       <c r="J40" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L40" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M40" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N40" s="9"/>
       <c r="O40" s="9"/>
       <c r="P40" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q40" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R40" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A40,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -7781,10 +7787,10 @@
         <v>9</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>184</v>
@@ -7800,24 +7806,24 @@
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L41" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N41" s="9"/>
       <c r="O41" s="9"/>
       <c r="P41" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q41" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R41" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A41,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -7852,10 +7858,10 @@
         <v>9</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>188</v>
@@ -7870,29 +7876,29 @@
         <v>64</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L42" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M42" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N42" s="9" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="O42" s="9"/>
       <c r="P42" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q42" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R42" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A42,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -7927,10 +7933,10 @@
         <v>9</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>193</v>
@@ -7945,29 +7951,29 @@
         <v>27</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K43" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L43" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M43" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="O43" s="9"/>
       <c r="P43" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q43" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R43" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A43,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -8002,10 +8008,10 @@
         <v>9</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>198</v>
@@ -8020,29 +8026,29 @@
         <v>27</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K44" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L44" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M44" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N44" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O44" s="9"/>
       <c r="P44" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q44" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R44" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A44,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -8077,10 +8083,10 @@
         <v>9</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>203</v>
@@ -8095,29 +8101,29 @@
         <v>27</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M45" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O45" s="9"/>
       <c r="P45" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q45" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R45" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A45,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -8152,10 +8158,10 @@
         <v>9</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>208</v>
@@ -8164,43 +8170,39 @@
         <v>209</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I46" s="9" t="s">
-        <v>328</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I46" s="9"/>
       <c r="J46" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L46" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M46" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="N46" s="9" t="s">
-        <v>329</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="N46" s="9"/>
       <c r="O46" s="9"/>
       <c r="P46" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q46" s="9" t="s">
-        <v>456</v>
+        <v>331</v>
       </c>
       <c r="R46" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A46,'Ground Truth'!$A$2:$A$105,0)),"")</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="S46" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$H$2:$H$105,MATCH(A46,'Ground Truth'!$A$2:$A$105,0)),"")</f>
-        <v>partial</v>
+        <v>executable</v>
       </c>
       <c r="T46" s="17">
         <f t="shared" si="4"/>
@@ -8216,7 +8218,7 @@
       </c>
       <c r="W46" s="17" t="str">
         <f t="shared" si="7"/>
-        <v>TN</v>
+        <v>TP</v>
       </c>
     </row>
     <row r="47" spans="1:23" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -8227,10 +8229,10 @@
         <v>9</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>213</v>
@@ -8245,29 +8247,29 @@
         <v>27</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K47" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L47" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M47" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="O47" s="9"/>
       <c r="P47" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q47" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R47" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A47,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -8302,10 +8304,10 @@
         <v>9</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>217</v>
@@ -8320,29 +8322,29 @@
         <v>27</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L48" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M48" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N48" s="9" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="O48" s="9"/>
       <c r="P48" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q48" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R48" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A48,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -8377,10 +8379,10 @@
         <v>9</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>221</v>
@@ -8396,24 +8398,24 @@
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N49" s="9"/>
       <c r="O49" s="9"/>
       <c r="P49" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q49" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R49" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A49,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -8448,10 +8450,10 @@
         <v>9</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>225</v>
@@ -8467,24 +8469,24 @@
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L50" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M50" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N50" s="9"/>
       <c r="O50" s="9"/>
       <c r="P50" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q50" s="9" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="R50" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A50,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -8519,10 +8521,10 @@
         <v>9</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>229</v>
@@ -8537,29 +8539,29 @@
         <v>27</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L51" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M51" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="O51" s="9"/>
       <c r="P51" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q51" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R51" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A51,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -8594,10 +8596,10 @@
         <v>9</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>233</v>
@@ -8612,29 +8614,29 @@
         <v>27</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K52" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L52" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M52" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N52" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O52" s="9"/>
       <c r="P52" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q52" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R52" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A52,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -8669,10 +8671,10 @@
         <v>9</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>237</v>
@@ -8687,29 +8689,29 @@
         <v>27</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L53" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M53" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O53" s="9"/>
       <c r="P53" s="9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q53" s="9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R53" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A53,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -8744,10 +8746,10 @@
         <v>241</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>10</v>
@@ -8763,24 +8765,24 @@
       </c>
       <c r="I54" s="9"/>
       <c r="J54" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K54" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L54" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M54" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N54" s="9"/>
       <c r="O54" s="9"/>
       <c r="P54" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q54" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R54" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A54,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -8815,10 +8817,10 @@
         <v>241</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>17</v>
@@ -8834,24 +8836,24 @@
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L55" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M55" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N55" s="9"/>
       <c r="O55" s="9"/>
       <c r="P55" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q55" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R55" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A55,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -8886,10 +8888,10 @@
         <v>241</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>22</v>
@@ -8905,24 +8907,24 @@
       </c>
       <c r="I56" s="9"/>
       <c r="J56" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K56" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L56" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M56" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N56" s="9"/>
       <c r="O56" s="9"/>
       <c r="P56" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q56" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R56" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A56,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -8957,10 +8959,10 @@
         <v>241</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>29</v>
@@ -8976,24 +8978,24 @@
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K57" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L57" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M57" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N57" s="9"/>
       <c r="O57" s="9"/>
       <c r="P57" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q57" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R57" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A57,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -9028,10 +9030,10 @@
         <v>241</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>34</v>
@@ -9047,24 +9049,24 @@
       </c>
       <c r="I58" s="9"/>
       <c r="J58" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K58" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L58" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M58" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N58" s="9"/>
       <c r="O58" s="9"/>
       <c r="P58" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q58" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R58" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A58,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -9099,10 +9101,10 @@
         <v>241</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>38</v>
@@ -9118,24 +9120,24 @@
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K59" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L59" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M59" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N59" s="9"/>
       <c r="O59" s="9"/>
       <c r="P59" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q59" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R59" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A59,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -9170,10 +9172,10 @@
         <v>241</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>42</v>
@@ -9189,24 +9191,24 @@
       </c>
       <c r="I60" s="9"/>
       <c r="J60" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K60" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L60" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M60" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N60" s="9"/>
       <c r="O60" s="9"/>
       <c r="P60" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q60" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R60" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A60,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -9241,10 +9243,10 @@
         <v>241</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>46</v>
@@ -9260,24 +9262,24 @@
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K61" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L61" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M61" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N61" s="9"/>
       <c r="O61" s="9"/>
       <c r="P61" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q61" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R61" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A61,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -9312,10 +9314,10 @@
         <v>241</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E62" s="9" t="s">
         <v>51</v>
@@ -9331,24 +9333,24 @@
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K62" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L62" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M62" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N62" s="9"/>
       <c r="O62" s="9"/>
       <c r="P62" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q62" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R62" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A62,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -9383,10 +9385,10 @@
         <v>241</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>56</v>
@@ -9401,29 +9403,29 @@
         <v>64</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K63" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L63" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M63" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="O63" s="9"/>
       <c r="P63" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q63" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R63" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A63,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -9458,10 +9460,10 @@
         <v>241</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E64" s="9" t="s">
         <v>60</v>
@@ -9477,24 +9479,24 @@
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K64" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L64" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M64" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N64" s="9"/>
       <c r="O64" s="9"/>
       <c r="P64" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q64" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R64" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A64,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -9529,10 +9531,10 @@
         <v>241</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>66</v>
@@ -9547,29 +9549,29 @@
         <v>64</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K65" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L65" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M65" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="O65" s="9"/>
       <c r="P65" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q65" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R65" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A65,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -9604,10 +9606,10 @@
         <v>241</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>71</v>
@@ -9623,24 +9625,24 @@
       </c>
       <c r="I66" s="9"/>
       <c r="J66" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K66" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L66" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M66" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N66" s="9"/>
       <c r="O66" s="9"/>
       <c r="P66" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q66" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R66" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A66,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -9675,10 +9677,10 @@
         <v>241</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>76</v>
@@ -9694,24 +9696,24 @@
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K67" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L67" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M67" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N67" s="9"/>
       <c r="O67" s="9"/>
       <c r="P67" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q67" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R67" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A67,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -9746,10 +9748,10 @@
         <v>241</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>81</v>
@@ -9765,24 +9767,24 @@
       </c>
       <c r="I68" s="9"/>
       <c r="J68" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K68" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L68" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M68" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N68" s="9"/>
       <c r="O68" s="9"/>
       <c r="P68" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q68" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R68" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A68,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -9817,10 +9819,10 @@
         <v>241</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>85</v>
@@ -9836,24 +9838,24 @@
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K69" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L69" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M69" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N69" s="9"/>
       <c r="O69" s="9"/>
       <c r="P69" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q69" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R69" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A69,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -9888,10 +9890,10 @@
         <v>241</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>90</v>
@@ -9906,29 +9908,29 @@
         <v>64</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J70" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K70" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L70" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M70" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N70" s="9" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="O70" s="9"/>
       <c r="P70" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q70" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R70" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A70,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -9963,10 +9965,10 @@
         <v>241</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>95</v>
@@ -9981,29 +9983,29 @@
         <v>64</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K71" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L71" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M71" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="O71" s="9"/>
       <c r="P71" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q71" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R71" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A71,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -10038,10 +10040,10 @@
         <v>241</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E72" s="9" t="s">
         <v>99</v>
@@ -10057,24 +10059,24 @@
       </c>
       <c r="I72" s="9"/>
       <c r="J72" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K72" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L72" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M72" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N72" s="9"/>
       <c r="O72" s="9"/>
       <c r="P72" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q72" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R72" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A72,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -10109,10 +10111,10 @@
         <v>241</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>104</v>
@@ -10128,24 +10130,24 @@
       </c>
       <c r="I73" s="9"/>
       <c r="J73" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K73" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L73" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M73" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N73" s="9"/>
       <c r="O73" s="9"/>
       <c r="P73" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q73" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R73" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A73,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -10180,10 +10182,10 @@
         <v>241</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E74" s="9" t="s">
         <v>109</v>
@@ -10199,24 +10201,24 @@
       </c>
       <c r="I74" s="9"/>
       <c r="J74" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K74" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L74" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M74" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N74" s="9"/>
       <c r="O74" s="9"/>
       <c r="P74" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q74" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R74" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A74,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -10251,10 +10253,10 @@
         <v>241</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>113</v>
@@ -10270,24 +10272,24 @@
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K75" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L75" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M75" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N75" s="9"/>
       <c r="O75" s="9"/>
       <c r="P75" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q75" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R75" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A75,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -10322,10 +10324,10 @@
         <v>241</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E76" s="9" t="s">
         <v>117</v>
@@ -10341,24 +10343,24 @@
       </c>
       <c r="I76" s="9"/>
       <c r="J76" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K76" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L76" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M76" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N76" s="9"/>
       <c r="O76" s="9"/>
       <c r="P76" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q76" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R76" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A76,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -10393,10 +10395,10 @@
         <v>241</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>122</v>
@@ -10412,24 +10414,24 @@
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K77" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L77" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M77" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N77" s="9"/>
       <c r="O77" s="9"/>
       <c r="P77" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q77" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R77" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A77,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -10464,10 +10466,10 @@
         <v>241</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E78" s="9" t="s">
         <v>125</v>
@@ -10483,24 +10485,24 @@
       </c>
       <c r="I78" s="9"/>
       <c r="J78" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K78" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L78" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M78" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N78" s="9"/>
       <c r="O78" s="9"/>
       <c r="P78" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q78" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R78" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A78,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -10535,10 +10537,10 @@
         <v>241</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>129</v>
@@ -10553,29 +10555,29 @@
         <v>64</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J79" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K79" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L79" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M79" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="O79" s="9"/>
       <c r="P79" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q79" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R79" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A79,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -10610,10 +10612,10 @@
         <v>241</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>132</v>
@@ -10629,24 +10631,24 @@
       </c>
       <c r="I80" s="9"/>
       <c r="J80" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K80" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L80" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M80" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N80" s="9"/>
       <c r="O80" s="9"/>
       <c r="P80" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q80" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R80" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A80,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -10681,10 +10683,10 @@
         <v>241</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>135</v>
@@ -10700,24 +10702,24 @@
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K81" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L81" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M81" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N81" s="9"/>
       <c r="O81" s="9"/>
       <c r="P81" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q81" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R81" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A81,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -10752,10 +10754,10 @@
         <v>241</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E82" s="9" t="s">
         <v>138</v>
@@ -10770,29 +10772,29 @@
         <v>64</v>
       </c>
       <c r="I82" s="9" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J82" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K82" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L82" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M82" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N82" s="9" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="O82" s="9"/>
       <c r="P82" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q82" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R82" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A82,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -10827,10 +10829,10 @@
         <v>241</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>142</v>
@@ -10846,24 +10848,24 @@
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K83" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L83" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M83" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N83" s="9"/>
       <c r="O83" s="9"/>
       <c r="P83" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q83" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R83" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A83,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -10898,10 +10900,10 @@
         <v>241</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E84" s="9" t="s">
         <v>147</v>
@@ -10917,24 +10919,24 @@
       </c>
       <c r="I84" s="9"/>
       <c r="J84" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K84" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L84" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M84" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N84" s="9"/>
       <c r="O84" s="9"/>
       <c r="P84" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q84" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R84" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A84,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -10969,10 +10971,10 @@
         <v>241</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>151</v>
@@ -10988,24 +10990,24 @@
       </c>
       <c r="I85" s="9"/>
       <c r="J85" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K85" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L85" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M85" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N85" s="9"/>
       <c r="O85" s="9"/>
       <c r="P85" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q85" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R85" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A85,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -11040,10 +11042,10 @@
         <v>241</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E86" s="9" t="s">
         <v>155</v>
@@ -11059,24 +11061,24 @@
       </c>
       <c r="I86" s="9"/>
       <c r="J86" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K86" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L86" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M86" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N86" s="9"/>
       <c r="O86" s="9"/>
       <c r="P86" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q86" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R86" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A86,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -11111,10 +11113,10 @@
         <v>241</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>159</v>
@@ -11129,29 +11131,29 @@
         <v>64</v>
       </c>
       <c r="I87" s="9" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J87" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K87" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L87" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M87" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="O87" s="9"/>
       <c r="P87" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q87" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R87" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A87,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -11186,10 +11188,10 @@
         <v>241</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E88" s="9" t="s">
         <v>164</v>
@@ -11205,24 +11207,24 @@
       </c>
       <c r="I88" s="9"/>
       <c r="J88" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K88" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L88" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M88" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N88" s="9"/>
       <c r="O88" s="9"/>
       <c r="P88" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q88" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R88" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A88,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -11257,10 +11259,10 @@
         <v>241</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>168</v>
@@ -11276,24 +11278,24 @@
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K89" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L89" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M89" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N89" s="9"/>
       <c r="O89" s="9"/>
       <c r="P89" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q89" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R89" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A89,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -11328,10 +11330,10 @@
         <v>241</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E90" s="9" t="s">
         <v>172</v>
@@ -11347,24 +11349,24 @@
       </c>
       <c r="I90" s="9"/>
       <c r="J90" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K90" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L90" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M90" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N90" s="9"/>
       <c r="O90" s="9"/>
       <c r="P90" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q90" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R90" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A90,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -11399,16 +11401,16 @@
         <v>241</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>176</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G91" s="9" t="s">
         <v>14</v>
@@ -11418,24 +11420,24 @@
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K91" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L91" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M91" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N91" s="9"/>
       <c r="O91" s="9"/>
       <c r="P91" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q91" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R91" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A91,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -11470,10 +11472,10 @@
         <v>241</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E92" s="9" t="s">
         <v>180</v>
@@ -11489,24 +11491,24 @@
       </c>
       <c r="I92" s="9"/>
       <c r="J92" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K92" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L92" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M92" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N92" s="9"/>
       <c r="O92" s="9"/>
       <c r="P92" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q92" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R92" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A92,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -11541,10 +11543,10 @@
         <v>241</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>184</v>
@@ -11560,24 +11562,24 @@
       </c>
       <c r="I93" s="9"/>
       <c r="J93" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K93" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L93" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M93" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N93" s="9"/>
       <c r="O93" s="9"/>
       <c r="P93" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q93" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R93" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A93,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -11612,10 +11614,10 @@
         <v>241</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E94" s="9" t="s">
         <v>188</v>
@@ -11631,24 +11633,24 @@
       </c>
       <c r="I94" s="9"/>
       <c r="J94" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K94" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L94" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M94" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N94" s="9"/>
       <c r="O94" s="9"/>
       <c r="P94" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q94" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R94" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A94,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -11683,10 +11685,10 @@
         <v>241</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>193</v>
@@ -11702,24 +11704,24 @@
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K95" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L95" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M95" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N95" s="9"/>
       <c r="O95" s="9"/>
       <c r="P95" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q95" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R95" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A95,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -11754,10 +11756,10 @@
         <v>241</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E96" s="9" t="s">
         <v>198</v>
@@ -11773,24 +11775,24 @@
       </c>
       <c r="I96" s="9"/>
       <c r="J96" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K96" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L96" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M96" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N96" s="9"/>
       <c r="O96" s="9"/>
       <c r="P96" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q96" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R96" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A96,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -11825,10 +11827,10 @@
         <v>241</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>203</v>
@@ -11844,24 +11846,24 @@
       </c>
       <c r="I97" s="9"/>
       <c r="J97" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K97" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L97" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M97" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N97" s="9"/>
       <c r="O97" s="9"/>
       <c r="P97" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q97" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R97" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A97,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -11896,10 +11898,10 @@
         <v>241</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E98" s="9" t="s">
         <v>208</v>
@@ -11915,24 +11917,24 @@
       </c>
       <c r="I98" s="9"/>
       <c r="J98" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K98" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L98" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M98" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N98" s="9"/>
       <c r="O98" s="9"/>
       <c r="P98" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q98" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R98" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A98,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -11943,7 +11945,7 @@
         <v>executable</v>
       </c>
       <c r="T98" s="17">
-        <f t="shared" ref="T98:T105" si="12">IF(S98="","",--(S98=H98))</f>
+        <f t="shared" ref="T98:T129" si="12">IF(S98="","",--(S98=H98))</f>
         <v>1</v>
       </c>
       <c r="U98" s="9" t="str">
@@ -11961,16 +11963,16 @@
     </row>
     <row r="99" spans="1:23" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B99" s="9" t="s">
         <v>241</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>213</v>
@@ -11986,24 +11988,24 @@
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K99" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L99" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M99" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N99" s="9"/>
       <c r="O99" s="9"/>
       <c r="P99" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q99" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R99" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A99,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -12032,16 +12034,16 @@
     </row>
     <row r="100" spans="1:23" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B100" s="9" t="s">
         <v>241</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E100" s="9" t="s">
         <v>217</v>
@@ -12057,24 +12059,24 @@
       </c>
       <c r="I100" s="9"/>
       <c r="J100" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K100" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L100" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M100" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N100" s="9"/>
       <c r="O100" s="9"/>
       <c r="P100" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q100" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R100" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A100,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -12103,16 +12105,16 @@
     </row>
     <row r="101" spans="1:23" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B101" s="9" t="s">
         <v>241</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>221</v>
@@ -12128,24 +12130,24 @@
       </c>
       <c r="I101" s="9"/>
       <c r="J101" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K101" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L101" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M101" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N101" s="9"/>
       <c r="O101" s="9"/>
       <c r="P101" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q101" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R101" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A101,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -12174,16 +12176,16 @@
     </row>
     <row r="102" spans="1:23" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B102" s="9" t="s">
         <v>241</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E102" s="9" t="s">
         <v>225</v>
@@ -12198,29 +12200,29 @@
         <v>64</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J102" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K102" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L102" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M102" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N102" s="9" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="O102" s="9"/>
       <c r="P102" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q102" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R102" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A102,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -12249,16 +12251,16 @@
     </row>
     <row r="103" spans="1:23" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B103" s="9" t="s">
         <v>241</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>229</v>
@@ -12274,24 +12276,24 @@
       </c>
       <c r="I103" s="9"/>
       <c r="J103" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K103" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L103" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M103" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N103" s="9"/>
       <c r="O103" s="9"/>
       <c r="P103" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q103" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R103" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A103,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -12320,16 +12322,16 @@
     </row>
     <row r="104" spans="1:23" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B104" s="9" t="s">
         <v>241</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E104" s="9" t="s">
         <v>233</v>
@@ -12345,24 +12347,24 @@
       </c>
       <c r="I104" s="9"/>
       <c r="J104" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K104" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L104" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M104" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N104" s="9"/>
       <c r="O104" s="9"/>
       <c r="P104" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q104" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R104" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A104,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -12391,16 +12393,16 @@
     </row>
     <row r="105" spans="1:23" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B105" s="9" t="s">
         <v>241</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>237</v>
@@ -12416,24 +12418,24 @@
       </c>
       <c r="I105" s="9"/>
       <c r="J105" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K105" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L105" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M105" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N105" s="9"/>
       <c r="O105" s="9"/>
       <c r="P105" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q105" s="9" t="s">
-        <v>457</v>
+        <v>334</v>
       </c>
       <c r="R105" s="17" t="str">
         <f>IFERROR(INDEX('Ground Truth'!$G$2:$G$105,MATCH(A105,'Ground Truth'!$A$2:$A$105,0)),"")</f>
@@ -12480,12 +12482,13 @@
     <col min="7" max="7" width="28" style="8" customWidth="1"/>
     <col min="8" max="8" width="36" style="8" customWidth="1"/>
     <col min="9" max="9" width="44" style="8" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" style="8"/>
+    <col min="10" max="10" width="8.88671875" style="8" customWidth="1"/>
     <col min="11" max="11" width="10" style="8" customWidth="1"/>
     <col min="12" max="12" width="34" style="8" customWidth="1"/>
     <col min="13" max="13" width="20" style="8" customWidth="1"/>
     <col min="14" max="14" width="44" style="8" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="8"/>
+    <col min="15" max="15" width="8.88671875" style="8" customWidth="1"/>
+    <col min="16" max="16384" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.3">
@@ -12493,32 +12496,32 @@
         <v>1</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="H1" s="24" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="I1" s="24" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="J1" s="25"/>
       <c r="K1" s="35" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L1" s="36"/>
       <c r="M1" s="36"/>
@@ -12529,41 +12532,41 @@
         <v>9</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E2" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G2" s="14">
         <v>649</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J2" s="14"/>
       <c r="K2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -12571,41 +12574,41 @@
         <v>9</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="G3" s="14">
         <v>1947</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J3" s="14"/>
       <c r="K3" s="14" t="s">
         <v>9</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="M3" s="14">
         <v>649</v>
       </c>
       <c r="N3" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -12613,41 +12616,41 @@
         <v>9</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>26</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="G4" s="14">
         <v>0</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J4" s="14"/>
       <c r="K4" s="14" t="s">
         <v>9</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M4" s="14">
         <v>649</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -12655,83 +12658,83 @@
         <v>9</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E5" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="G5" s="14">
         <v>649</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J5" s="14"/>
       <c r="K5" s="14" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M5" s="14">
         <v>3</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G6" s="14">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>459</v>
+        <v>370</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="J6" s="14"/>
       <c r="K6" s="14" t="s">
         <v>9</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="M6" s="14">
         <v>1947</v>
       </c>
       <c r="N6" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -12739,41 +12742,41 @@
         <v>9</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>26</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="G7" s="14">
         <v>0</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J7" s="14"/>
       <c r="K7" s="14" t="s">
         <v>9</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="M7" s="14">
         <v>1947</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -12781,41 +12784,41 @@
         <v>9</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="G8" s="14">
         <v>649</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J8" s="14"/>
       <c r="K8" s="14" t="s">
         <v>9</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="M8" s="14">
         <v>649</v>
       </c>
       <c r="N8" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -12823,41 +12826,41 @@
         <v>9</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="G9" s="14">
         <v>649</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J9" s="14"/>
       <c r="K9" s="14" t="s">
         <v>9</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="M9" s="14">
         <v>0</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -12865,41 +12868,41 @@
         <v>9</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="G10" s="14">
         <v>649</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J10" s="14"/>
       <c r="K10" s="14" t="s">
         <v>9</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="M10" s="14">
         <v>0</v>
       </c>
       <c r="N10" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -12907,41 +12910,41 @@
         <v>9</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="G11" s="14">
         <v>649</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J11" s="14"/>
       <c r="K11" s="14" t="s">
         <v>9</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="M11" s="14">
         <v>0</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -12949,41 +12952,41 @@
         <v>9</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="G12" s="14">
         <v>3</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="14" t="s">
         <v>9</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="M12" s="14">
         <v>0</v>
       </c>
       <c r="N12" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -12991,41 +12994,41 @@
         <v>9</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="G13" s="14">
         <v>0</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J13" s="14"/>
       <c r="K13" s="14" t="s">
         <v>9</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="M13" s="14">
         <v>0</v>
       </c>
       <c r="N13" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -13033,83 +13036,83 @@
         <v>9</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>26</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="G14" s="14">
         <v>0</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J14" s="14"/>
       <c r="K14" s="14" t="s">
         <v>9</v>
       </c>
       <c r="L14" s="14" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="M14" s="14">
         <v>649</v>
       </c>
       <c r="N14" s="14" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="G15" s="14">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>359</v>
+        <v>398</v>
       </c>
       <c r="J15" s="14"/>
       <c r="K15" s="14" t="s">
         <v>9</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="M15" s="14">
         <v>649</v>
       </c>
       <c r="N15" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -13117,41 +13120,41 @@
         <v>9</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="G16" s="14">
         <v>649</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J16" s="14"/>
       <c r="K16" s="14" t="s">
         <v>9</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="M16" s="14">
         <v>649</v>
       </c>
       <c r="N16" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -13159,41 +13162,41 @@
         <v>9</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="G17" s="14">
         <v>1947</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J17" s="14"/>
       <c r="K17" s="14" t="s">
         <v>9</v>
       </c>
       <c r="L17" s="14" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="M17" s="14">
         <v>649</v>
       </c>
       <c r="N17" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -13201,41 +13204,41 @@
         <v>9</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E18" s="16" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J18" s="14"/>
       <c r="K18" s="14" t="s">
         <v>9</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="M18" s="14">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N18" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -13243,41 +13246,41 @@
         <v>9</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="E19" s="16" t="s">
         <v>26</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>461</v>
+        <v>410</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J19" s="14"/>
       <c r="K19" s="14" t="s">
         <v>9</v>
       </c>
       <c r="L19" s="14" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M19" s="14">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N19" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -13285,41 +13288,41 @@
         <v>241</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>26</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G20" s="14">
         <v>0</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J20" s="14"/>
       <c r="K20" s="14" t="s">
         <v>9</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="M20" s="14">
         <v>0</v>
       </c>
       <c r="N20" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -13327,41 +13330,41 @@
         <v>241</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="G21" s="14">
         <v>11445</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J21" s="14"/>
       <c r="K21" s="14" t="s">
         <v>241</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="M21" s="14">
         <v>2498</v>
       </c>
       <c r="N21" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -13369,41 +13372,41 @@
         <v>241</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>26</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="G22" s="14">
         <v>0</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J22" s="14"/>
       <c r="K22" s="14" t="s">
         <v>241</v>
       </c>
       <c r="L22" s="14" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M22" s="14">
         <v>2498</v>
       </c>
       <c r="N22" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -13411,41 +13414,41 @@
         <v>241</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="G23" s="14">
         <v>2498</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J23" s="14"/>
       <c r="K23" s="14" t="s">
         <v>241</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M23" s="14">
         <v>10</v>
       </c>
       <c r="N23" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -13453,41 +13456,41 @@
         <v>241</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G24" s="14">
         <v>2360</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>459</v>
+        <v>370</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J24" s="14"/>
       <c r="K24" s="14" t="s">
         <v>241</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="M24" s="14">
         <v>11451</v>
       </c>
       <c r="N24" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -13495,41 +13498,41 @@
         <v>241</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="G25" s="14">
         <v>515832</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J25" s="14"/>
       <c r="K25" s="14" t="s">
         <v>241</v>
       </c>
       <c r="L25" s="14" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="M25" s="14">
         <v>11445</v>
       </c>
       <c r="N25" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -13537,41 +13540,41 @@
         <v>241</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E26" s="16" t="s">
         <v>26</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="G26" s="14">
         <v>0</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J26" s="14"/>
       <c r="K26" s="14" t="s">
         <v>241</v>
       </c>
       <c r="L26" s="14" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="M26" s="14">
         <v>2498</v>
       </c>
       <c r="N26" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -13579,41 +13582,41 @@
         <v>241</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="G27" s="14">
         <v>2498</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J27" s="14"/>
       <c r="K27" s="14" t="s">
         <v>241</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="M27" s="14">
         <v>11451</v>
       </c>
       <c r="N27" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -13621,41 +13624,41 @@
         <v>241</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>26</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="G28" s="14">
         <v>0</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J28" s="14"/>
       <c r="K28" s="14" t="s">
         <v>241</v>
       </c>
       <c r="L28" s="14" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="M28" s="14">
         <v>515832</v>
       </c>
       <c r="N28" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -13663,41 +13666,41 @@
         <v>241</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="G29" s="14">
         <v>2498</v>
       </c>
       <c r="H29" s="14" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J29" s="14"/>
       <c r="K29" s="14" t="s">
         <v>241</v>
       </c>
       <c r="L29" s="14" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="M29" s="14">
         <v>515832</v>
       </c>
       <c r="N29" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -13705,41 +13708,41 @@
         <v>241</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="G30" s="14">
         <v>10</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J30" s="14"/>
       <c r="K30" s="14" t="s">
         <v>241</v>
       </c>
       <c r="L30" s="14" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="M30" s="14">
         <v>42</v>
       </c>
       <c r="N30" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -13747,41 +13750,41 @@
         <v>241</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E31" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="G31" s="14">
         <v>2482</v>
       </c>
       <c r="H31" s="14" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J31" s="14"/>
       <c r="K31" s="14" t="s">
         <v>241</v>
       </c>
       <c r="L31" s="14" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="M31" s="14">
         <v>223</v>
       </c>
       <c r="N31" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -13789,41 +13792,41 @@
         <v>241</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="E32" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="G32" s="14">
         <v>223</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J32" s="14"/>
       <c r="K32" s="14" t="s">
         <v>241</v>
       </c>
       <c r="L32" s="14" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="M32" s="14">
         <v>0</v>
       </c>
       <c r="N32" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -13831,41 +13834,41 @@
         <v>241</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="G33" s="14">
         <v>2498</v>
       </c>
       <c r="H33" s="14" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J33" s="14"/>
       <c r="K33" s="14" t="s">
         <v>241</v>
       </c>
       <c r="L33" s="14" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="M33" s="14">
         <v>0</v>
       </c>
       <c r="N33" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -13873,41 +13876,41 @@
         <v>241</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="E34" s="16" t="s">
         <v>26</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="G34" s="14">
         <v>0</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J34" s="14"/>
       <c r="K34" s="14" t="s">
         <v>241</v>
       </c>
       <c r="L34" s="14" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="M34" s="14">
         <v>0</v>
       </c>
       <c r="N34" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
@@ -13915,41 +13918,41 @@
         <v>241</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="E35" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="G35" s="14">
         <v>11451</v>
       </c>
       <c r="H35" s="14" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J35" s="14"/>
       <c r="K35" s="14" t="s">
         <v>241</v>
       </c>
       <c r="L35" s="14" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="M35" s="14">
         <v>0</v>
       </c>
       <c r="N35" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -13957,41 +13960,41 @@
         <v>241</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J36" s="14"/>
       <c r="K36" s="14" t="s">
         <v>241</v>
       </c>
       <c r="L36" s="14" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="M36" s="14">
         <v>2498</v>
       </c>
       <c r="N36" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -13999,41 +14002,41 @@
         <v>241</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="E37" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="H37" s="14" t="s">
-        <v>461</v>
+        <v>410</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J37" s="14"/>
       <c r="K37" s="14" t="s">
         <v>241</v>
       </c>
       <c r="L37" s="14" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M37" s="14">
         <v>2360</v>
       </c>
       <c r="N37" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
@@ -14051,13 +14054,13 @@
         <v>241</v>
       </c>
       <c r="L38" s="14" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="M38" s="14">
         <v>2482</v>
       </c>
       <c r="N38" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -14080,12 +14083,13 @@
     <col min="4" max="4" width="15" style="8" customWidth="1"/>
     <col min="5" max="5" width="18" style="8" customWidth="1"/>
     <col min="6" max="6" width="15" style="8" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="8"/>
+    <col min="7" max="7" width="8.88671875" style="8" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="40" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="B1" s="39"/>
       <c r="C1" s="39"/>
@@ -14095,7 +14099,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="38" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="B2" s="39"/>
       <c r="C2" s="39"/>
@@ -14108,170 +14112,170 @@
     </row>
     <row r="4" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="30" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="28" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTA('Machine Results'!A2:A105)</f>
         <v>104</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>454</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="28" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF('Machine Results'!W2:W105,"TP")</f>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="28" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('Machine Results'!W2:W105,"TN")</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="28" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTIF('Machine Results'!W2:W105,"FP")</f>
         <v>0</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="28" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTIF('Machine Results'!W2:W105,"FN")</f>
         <v>0</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="28" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="B10" s="29">
         <f>IF(B5=0,"",(B6+B7)/B5)</f>
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="28" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="B11" s="29">
         <f>IF((B6+B8)=0,"",B6/(B6+B8))</f>
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="28" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="B12" s="29">
         <f>IF((B6+B9)=0,"",B6/(B6+B9))</f>
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="B13" s="29">
         <f>IF((B11+B12)=0,"",2*B11*B12/(B11+B12))</f>
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="28" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="B14" s="2">
         <f>COUNTIF('Machine Results'!T2:T105,1)</f>
         <v>104</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="28" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="B15" s="29">
         <f>IF(B5=0,"",B14/B5)</f>
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="33" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="F19" s="33" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -14284,11 +14288,11 @@
       </c>
       <c r="C20" s="32">
         <f>COUNTIFS('Machine Results'!B:B,A20,'Machine Results'!H:H,"executable")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D20" s="32">
         <f>COUNTIFS('Machine Results'!B:B,A20,'Machine Results'!H:H,"partial")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20" s="32">
         <f>COUNTIFS('Machine Results'!B:B,A20,'Machine Results'!H:H,"insufficient_data")</f>
@@ -14344,82 +14348,82 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="34" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="34" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="34" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="28.8" customHeight="1" x14ac:dyDescent="0.3"/>
